--- a/data/WP17/WP17_sachgebiete_AfD_zeitreihe.xlsx
+++ b/data/WP17/WP17_sachgebiete_AfD_zeitreihe.xlsx
@@ -2122,13 +2122,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8AB46B0D-EE2E-4B33-88B0-F1D21F465F02}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{30264192-9BC6-4654-856B-9C12205A3B4B}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{023B650B-628C-43F5-81F2-29353DC83C43}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AB8D5BBE-45F6-4F5F-9128-CB3C07DBDF49}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2C37C9B4-2D3A-4355-9C86-4264D18983BF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{31EC4038-417A-4777-ACE0-5DC32BE310D9}"/>
 </file>
--- a/data/WP17/WP17_sachgebiete_AfD_zeitreihe.xlsx
+++ b/data/WP17/WP17_sachgebiete_AfD_zeitreihe.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
   <si>
     <t xml:space="preserve">periode</t>
   </si>
@@ -56,103 +56,97 @@
     <t xml:space="preserve">Ideologien</t>
   </si>
   <si>
+    <t xml:space="preserve">Frauen, Männer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arbeitsmarkt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gesundheitsschutz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sport</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gerichte und Staatsanwaltschaften</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wohnungswesen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Schulen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Natur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Polizei</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tier, Tierschutz, Tierhaltung</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kommunale Angelegenheiten</t>
   </si>
   <si>
-    <t xml:space="preserve">Arbeitsmarkt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gesundheitsschutz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bauwesen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Frauen, Männer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sport</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Öffentlicher Dienst</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wohnungswesen</t>
+    <t xml:space="preserve">Arbeit und Beschäftigung</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alte Menschen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Religionsgemeinschaften</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Straßenverkehr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Landesregierung</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Öffentliches Vermögen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kunst, Kultur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Freizeit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gesundheit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Allgemeinbildende Schulen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Erneuerbare Energien</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Klima</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Informations- und Kommunikationstechnologien</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Katastrophen- und Zivilschutz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kinder, Jugendliche</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Justizvollzug</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agrarmarkt</t>
   </si>
   <si>
     <t xml:space="preserve">Gesundheitseinrichtungen</t>
   </si>
   <si>
-    <t xml:space="preserve">Polizei</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tier, Tierschutz, Tierhaltung</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arbeit und Beschäftigung</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gerichte und Staatsanwaltschaften</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alte Menschen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Schulen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Landesregierung</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Straßenverkehr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Öffentliches Vermögen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kunst, Kultur</t>
+    <t xml:space="preserve">Ordnungsrecht</t>
   </si>
   <si>
     <t xml:space="preserve">Öffentlicher Haushalt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Freizeit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gesundheit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Landwirtschaft</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Erneuerbare Energien</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Allgemeinbildende Schulen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stiftung</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Informations- und Kommunikationstechnologien</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Katastrophen- und Zivilschutz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kinder, Jugendliche</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Justizvollzug</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Agrarmarkt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Klima</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ordnungsrecht</t>
   </si>
   <si>
     <t xml:space="preserve">Rundfunk, Fernsehen</t>
@@ -562,7 +556,7 @@
         <v>10</v>
       </c>
       <c r="C3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D3" t="s">
         <v>7</v>
@@ -585,7 +579,7 @@
         <v>10</v>
       </c>
       <c r="C4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D4" t="s">
         <v>7</v>
@@ -631,19 +625,19 @@
         <v>7</v>
       </c>
       <c r="C6" t="n">
+        <v>7</v>
+      </c>
+      <c r="D6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" t="n">
         <v>6</v>
-      </c>
-      <c r="D6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E6" t="n">
-        <v>4</v>
       </c>
       <c r="F6" t="s">
         <v>14</v>
       </c>
       <c r="G6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -654,19 +648,19 @@
         <v>7</v>
       </c>
       <c r="C7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D7" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F7" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -686,10 +680,10 @@
         <v>3</v>
       </c>
       <c r="F8" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -700,7 +694,7 @@
         <v>7</v>
       </c>
       <c r="C9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D9" t="s">
         <v>10</v>
@@ -709,7 +703,7 @@
         <v>5</v>
       </c>
       <c r="F9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="G9" t="n">
         <v>3</v>
@@ -720,19 +714,19 @@
         <v>43132</v>
       </c>
       <c r="B10" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C10" t="n">
         <v>2</v>
       </c>
       <c r="D10" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F10" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="G10" t="n">
         <v>1</v>
@@ -743,19 +737,19 @@
         <v>43160</v>
       </c>
       <c r="B11" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C11" t="n">
         <v>5</v>
       </c>
       <c r="D11" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F11" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G11" t="n">
         <v>4</v>
@@ -769,16 +763,16 @@
         <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D12" t="s">
         <v>7</v>
       </c>
       <c r="E12" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G12" t="n">
         <v>3</v>
@@ -789,22 +783,22 @@
         <v>43221</v>
       </c>
       <c r="B13" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D13" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -815,16 +809,16 @@
         <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D14" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="E14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F14" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="G14" t="n">
         <v>3</v>
@@ -838,16 +832,16 @@
         <v>7</v>
       </c>
       <c r="C15" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D15" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F15" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G15" t="n">
         <v>2</v>
@@ -870,7 +864,7 @@
         <v>3</v>
       </c>
       <c r="F16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G16" t="n">
         <v>3</v>
@@ -887,7 +881,7 @@
         <v>4</v>
       </c>
       <c r="D17" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="E17" t="n">
         <v>4</v>
@@ -907,13 +901,13 @@
         <v>7</v>
       </c>
       <c r="C18" t="n">
+        <v>5</v>
+      </c>
+      <c r="D18" t="s">
+        <v>10</v>
+      </c>
+      <c r="E18" t="n">
         <v>4</v>
-      </c>
-      <c r="D18" t="s">
-        <v>10</v>
-      </c>
-      <c r="E18" t="n">
-        <v>3</v>
       </c>
       <c r="F18" t="s">
         <v>13</v>
@@ -936,7 +930,7 @@
         <v>7</v>
       </c>
       <c r="E19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F19" t="s">
         <v>25</v>
@@ -953,16 +947,16 @@
         <v>10</v>
       </c>
       <c r="C20" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D20" t="s">
+        <v>18</v>
+      </c>
+      <c r="E20" t="n">
+        <v>7</v>
+      </c>
+      <c r="F20" t="s">
         <v>26</v>
-      </c>
-      <c r="E20" t="n">
-        <v>7</v>
-      </c>
-      <c r="F20" t="s">
-        <v>27</v>
       </c>
       <c r="G20" t="n">
         <v>1</v>
@@ -973,7 +967,7 @@
         <v>43466</v>
       </c>
       <c r="B21" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
         <v>7</v>
@@ -1008,7 +1002,7 @@
         <v>2</v>
       </c>
       <c r="F22" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G22" t="n">
         <v>2</v>
@@ -1019,7 +1013,7 @@
         <v>43525</v>
       </c>
       <c r="B23" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C23" t="n">
         <v>5</v>
@@ -1031,7 +1025,7 @@
         <v>3</v>
       </c>
       <c r="F23" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G23" t="n">
         <v>3</v>
@@ -1045,10 +1039,10 @@
         <v>7</v>
       </c>
       <c r="C24" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D24" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E24" t="n">
         <v>4</v>
@@ -1074,10 +1068,10 @@
         <v>7</v>
       </c>
       <c r="E25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F25" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="G25" t="n">
         <v>2</v>
@@ -1091,7 +1085,7 @@
         <v>7</v>
       </c>
       <c r="C26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D26" t="s">
         <v>29</v>
@@ -1100,7 +1094,7 @@
         <v>2</v>
       </c>
       <c r="F26" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="G26" t="n">
         <v>2</v>
@@ -1114,16 +1108,16 @@
         <v>7</v>
       </c>
       <c r="C27" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D27" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E27" t="n">
         <v>8</v>
       </c>
       <c r="F27" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G27" t="n">
         <v>2</v>
@@ -1134,22 +1128,22 @@
         <v>43678</v>
       </c>
       <c r="B28" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C28" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D28" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E28" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F28" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G28" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29">
@@ -1157,22 +1151,22 @@
         <v>43709</v>
       </c>
       <c r="B29" t="s">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="C29" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D29" t="s">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="E29" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F29" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G29" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30">
@@ -1180,19 +1174,19 @@
         <v>43739</v>
       </c>
       <c r="B30" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C30" t="n">
         <v>3</v>
       </c>
       <c r="D30" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F30" t="s">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="G30" t="n">
         <v>2</v>
@@ -1209,13 +1203,13 @@
         <v>54</v>
       </c>
       <c r="D31" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="E31" t="n">
         <v>53</v>
       </c>
       <c r="F31" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="G31" t="n">
         <v>53</v>
@@ -1238,7 +1232,7 @@
         <v>3</v>
       </c>
       <c r="F32" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G32" t="n">
         <v>3</v>
@@ -1252,7 +1246,7 @@
         <v>7</v>
       </c>
       <c r="C33" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D33" t="s">
         <v>10</v>
@@ -1261,7 +1255,7 @@
         <v>3</v>
       </c>
       <c r="F33" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="G33" t="n">
         <v>2</v>
@@ -1275,7 +1269,7 @@
         <v>7</v>
       </c>
       <c r="C34" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D34" t="s">
         <v>10</v>
@@ -1284,7 +1278,7 @@
         <v>4</v>
       </c>
       <c r="F34" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G34" t="n">
         <v>3</v>
@@ -1295,7 +1289,7 @@
         <v>43891</v>
       </c>
       <c r="B35" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C35" t="n">
         <v>3</v>
@@ -1307,7 +1301,7 @@
         <v>2</v>
       </c>
       <c r="F35" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="G35" t="n">
         <v>1</v>
@@ -1324,13 +1318,13 @@
         <v>38</v>
       </c>
       <c r="D36" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E36" t="n">
         <v>29</v>
       </c>
       <c r="F36" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G36" t="n">
         <v>3</v>
@@ -1347,13 +1341,13 @@
         <v>14</v>
       </c>
       <c r="D37" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E37" t="n">
         <v>13</v>
       </c>
       <c r="F37" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="G37" t="n">
         <v>8</v>
@@ -1364,7 +1358,7 @@
         <v>43983</v>
       </c>
       <c r="B38" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="C38" t="n">
         <v>46</v>
@@ -1387,19 +1381,19 @@
         <v>44013</v>
       </c>
       <c r="B39" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="C39" t="n">
         <v>54</v>
       </c>
       <c r="D39" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="E39" t="n">
         <v>53</v>
       </c>
       <c r="F39" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="G39" t="n">
         <v>34</v>
@@ -1422,7 +1416,7 @@
         <v>2</v>
       </c>
       <c r="F40" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="G40" t="n">
         <v>2</v>
@@ -1456,19 +1450,19 @@
         <v>44105</v>
       </c>
       <c r="B42" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="C42" t="n">
         <v>49</v>
       </c>
       <c r="D42" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E42" t="n">
         <v>44</v>
       </c>
       <c r="F42" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G42" t="n">
         <v>9</v>
@@ -1485,13 +1479,13 @@
         <v>3</v>
       </c>
       <c r="D43" t="s">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="E43" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F43" t="s">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="G43" t="n">
         <v>2</v>
@@ -1548,13 +1542,13 @@
         <v>44228</v>
       </c>
       <c r="B46" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C46" t="n">
         <v>30</v>
       </c>
       <c r="D46" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E46" t="n">
         <v>7</v>
@@ -1577,13 +1571,13 @@
         <v>59</v>
       </c>
       <c r="D47" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E47" t="n">
         <v>57</v>
       </c>
       <c r="F47" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="G47" t="n">
         <v>7</v>
@@ -1623,13 +1617,13 @@
         <v>56</v>
       </c>
       <c r="D49" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E49" t="n">
         <v>54</v>
       </c>
       <c r="F49" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G49" t="n">
         <v>7</v>
@@ -1649,10 +1643,10 @@
         <v>10</v>
       </c>
       <c r="E50" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F50" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G50" t="n">
         <v>2</v>
@@ -1669,13 +1663,13 @@
         <v>5</v>
       </c>
       <c r="D51" t="s">
-        <v>51</v>
+        <v>10</v>
       </c>
       <c r="E51" t="n">
         <v>1</v>
       </c>
       <c r="F51" t="s">
-        <v>22</v>
+        <v>49</v>
       </c>
       <c r="G51" t="n">
         <v>1</v>
@@ -1698,7 +1692,7 @@
         <v>6</v>
       </c>
       <c r="F52" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="G52" t="n">
         <v>4</v>
@@ -1732,13 +1726,13 @@
         <v>44470</v>
       </c>
       <c r="B54" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C54" t="n">
         <v>40</v>
       </c>
       <c r="D54" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="E54" t="n">
         <v>39</v>
@@ -1755,7 +1749,7 @@
         <v>44501</v>
       </c>
       <c r="B55" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C55" t="n">
         <v>3</v>
@@ -1767,7 +1761,7 @@
         <v>2</v>
       </c>
       <c r="F55" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G55" t="n">
         <v>2</v>
@@ -1784,13 +1778,13 @@
         <v>5</v>
       </c>
       <c r="D56" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E56" t="n">
         <v>3</v>
       </c>
       <c r="F56" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="G56" t="n">
         <v>1</v>
@@ -1853,7 +1847,7 @@
         <v>7</v>
       </c>
       <c r="D59" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E59" t="n">
         <v>4</v>
@@ -1870,7 +1864,7 @@
         <v>44652</v>
       </c>
       <c r="B60" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C60" t="n">
         <v>1</v>
@@ -1882,7 +1876,7 @@
         <v>1</v>
       </c>
       <c r="F60" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="G60" t="n">
         <v>1</v>
@@ -2122,13 +2116,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{30264192-9BC6-4654-856B-9C12205A3B4B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F50A9CB1-13D1-4C03-8C08-428A00CADB1D}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AB8D5BBE-45F6-4F5F-9128-CB3C07DBDF49}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{15259FBB-C2F2-48C4-85A6-3E7848A5034E}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{31EC4038-417A-4777-ACE0-5DC32BE310D9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F6AF433F-E47F-440E-80CD-C5058A415BEF}"/>
 </file>
--- a/data/WP17/WP17_sachgebiete_AfD_zeitreihe.xlsx
+++ b/data/WP17/WP17_sachgebiete_AfD_zeitreihe.xlsx
@@ -2116,13 +2116,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F50A9CB1-13D1-4C03-8C08-428A00CADB1D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{33264FBA-2760-4478-A6A0-74C5735B659A}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{15259FBB-C2F2-48C4-85A6-3E7848A5034E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DF18C322-2242-4B17-B210-DC4DEA9089E4}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F6AF433F-E47F-440E-80CD-C5058A415BEF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{04F22C4A-4579-400B-8E5B-B67E3880C909}"/>
 </file>